--- a/artfynd/A 13761-2020 artfynd.xlsx
+++ b/artfynd/A 13761-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123203283</v>
+        <v>123203296</v>
       </c>
       <c r="B2" t="n">
         <v>106715</v>
@@ -710,13 +710,13 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>370830</v>
+        <v>370825</v>
       </c>
       <c r="R2" t="n">
-        <v>6315074</v>
+        <v>6315067</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>SKOGVÄG SAND O GRUS</t>
+          <t>SKOGSVÄG BLANDSKOG</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123203296</v>
+        <v>123203283</v>
       </c>
       <c r="B3" t="n">
         <v>106715</v>
@@ -830,13 +830,13 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>370825</v>
+        <v>370830</v>
       </c>
       <c r="R3" t="n">
-        <v>6315067</v>
+        <v>6315074</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>SKOGSVÄG BLANDSKOG</t>
+          <t>SKOGVÄG SAND O GRUS</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 13761-2020 artfynd.xlsx
+++ b/artfynd/A 13761-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123203296</v>
       </c>
       <c r="B2" t="n">
-        <v>106715</v>
+        <v>106894</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>123203283</v>
       </c>
       <c r="B3" t="n">
-        <v>106715</v>
+        <v>106894</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 13761-2020 artfynd.xlsx
+++ b/artfynd/A 13761-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123203283</v>
       </c>
       <c r="B2" t="n">
-        <v>106949</v>
+        <v>106956</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>123203296</v>
       </c>
       <c r="B3" t="n">
-        <v>106949</v>
+        <v>106956</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13761-2020 artfynd.xlsx
+++ b/artfynd/A 13761-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123203283</v>
+        <v>123203296</v>
       </c>
       <c r="B2" t="n">
-        <v>106956</v>
+        <v>106959</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,13 +705,13 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>370830</v>
+        <v>370825</v>
       </c>
       <c r="R2" t="n">
-        <v>6315074</v>
+        <v>6315067</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>SKOGVÄG SAND O GRUS</t>
+          <t>SKOGSVÄG BLANDSKOG</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123203296</v>
+        <v>123203283</v>
       </c>
       <c r="B3" t="n">
-        <v>106956</v>
+        <v>106959</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,13 +820,13 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>370825</v>
+        <v>370830</v>
       </c>
       <c r="R3" t="n">
-        <v>6315067</v>
+        <v>6315074</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>SKOGSVÄG BLANDSKOG</t>
+          <t>SKOGVÄG SAND O GRUS</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 13761-2020 artfynd.xlsx
+++ b/artfynd/A 13761-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123203296</v>
       </c>
       <c r="B2" t="n">
-        <v>106959</v>
+        <v>106963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>123203283</v>
       </c>
       <c r="B3" t="n">
-        <v>106959</v>
+        <v>106963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13761-2020 artfynd.xlsx
+++ b/artfynd/A 13761-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123203296</v>
+        <v>123203283</v>
       </c>
       <c r="B2" t="n">
-        <v>106963</v>
+        <v>106964</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,13 +705,13 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>370825</v>
+        <v>370830</v>
       </c>
       <c r="R2" t="n">
-        <v>6315067</v>
+        <v>6315074</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>SKOGSVÄG BLANDSKOG</t>
+          <t>SKOGVÄG SAND O GRUS</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123203283</v>
+        <v>123203296</v>
       </c>
       <c r="B3" t="n">
-        <v>106963</v>
+        <v>106964</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,13 +820,13 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>370830</v>
+        <v>370825</v>
       </c>
       <c r="R3" t="n">
-        <v>6315074</v>
+        <v>6315067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>SKOGVÄG SAND O GRUS</t>
+          <t>SKOGSVÄG BLANDSKOG</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
